--- a/dados/3.xlsx
+++ b/dados/3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F1909D-CF82-4CA1-B7D8-D48F30A3B731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE79BF11-9B4D-42E9-AA6E-F7131CB6B1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="54">
   <si>
     <t>Mês</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>MARNEI LIMA MORAIS</t>
+  </si>
+  <si>
+    <t>DAYANE MACLEYNE PEREIRA FREITAS DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -549,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F494"/>
+  <dimension ref="A1:F507"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -10420,7 +10423,267 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A494" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B494" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C494" s="4">
+        <v>98</v>
+      </c>
+      <c r="D494" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E494" s="5">
+        <v>100362.6</v>
+      </c>
+      <c r="F494" s="4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A495" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B495" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C495" s="4">
+        <v>95</v>
+      </c>
+      <c r="D495" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E495" s="5">
+        <v>31687.23</v>
+      </c>
+      <c r="F495" s="4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A496" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C496" s="4">
+        <v>100</v>
+      </c>
+      <c r="D496" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E496" s="5">
+        <v>26415.55</v>
+      </c>
+      <c r="F496" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A497" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C497" s="4">
+        <v>129</v>
+      </c>
+      <c r="D497" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E497" s="5">
+        <v>16582.669999999998</v>
+      </c>
+      <c r="F497" s="4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A498" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C498" s="4">
+        <v>58</v>
+      </c>
+      <c r="D498" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E498" s="5">
+        <v>15066.70002</v>
+      </c>
+      <c r="F498" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A499" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B499" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C499" s="4">
+        <v>81</v>
+      </c>
+      <c r="D499" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E499" s="5">
+        <v>13110.21</v>
+      </c>
+      <c r="F499" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A500" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B500" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C500" s="4">
+        <v>104</v>
+      </c>
+      <c r="D500" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E500" s="5">
+        <v>8823.2800000000007</v>
+      </c>
+      <c r="F500" s="4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A501" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C501" s="4">
+        <v>34</v>
+      </c>
+      <c r="D501" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E501" s="5">
+        <v>5528.73</v>
+      </c>
+      <c r="F501" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A502" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B502" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C502" s="4">
+        <v>6</v>
+      </c>
+      <c r="D502" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E502" s="5">
+        <v>4096.38</v>
+      </c>
+      <c r="F502" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A503" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B503" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C503" s="4">
+        <v>85</v>
+      </c>
+      <c r="D503" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E503" s="5">
+        <v>3734.11</v>
+      </c>
+      <c r="F503" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A504" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B504" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C504" s="4">
+        <v>137</v>
+      </c>
+      <c r="D504" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E504" s="5">
+        <v>3249.2</v>
+      </c>
+      <c r="F504" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A505" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B505" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C505" s="4">
+        <v>141</v>
+      </c>
+      <c r="D505" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E505" s="5">
+        <v>734.46</v>
+      </c>
+      <c r="F505" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A506" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B506" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C506" s="4">
+        <v>4</v>
+      </c>
+      <c r="D506" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E506" s="5">
+        <v>82.13</v>
+      </c>
+      <c r="F506" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
